--- a/inputs/templates/TEMPLATE_FONDO_USD_MONEY_MARKET.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_USD_MONEY_MARKET.xlsx
@@ -2393,11 +2393,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="82051744"/>
-        <c:axId val="25742030"/>
+        <c:axId val="31899155"/>
+        <c:axId val="73382495"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="82051744"/>
+        <c:axId val="31899155"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2429,7 +2429,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25742030"/>
+        <c:crossAx val="73382495"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -2440,7 +2440,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="25742030"/>
+        <c:axId val="73382495"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2516,7 +2516,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82051744"/>
+        <c:crossAx val="31899155"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -18110,7 +18110,7 @@
         <v>46142</v>
       </c>
       <c r="B244" s="2" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="F244" s="67" t="n">
         <v>46142</v>

--- a/inputs/templates/TEMPLATE_FONDO_USD_MONEY_MARKET.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_USD_MONEY_MARKET.xlsx
@@ -2393,11 +2393,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="31899155"/>
-        <c:axId val="73382495"/>
+        <c:axId val="49003960"/>
+        <c:axId val="80090288"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="31899155"/>
+        <c:axId val="49003960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2429,7 +2429,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73382495"/>
+        <c:crossAx val="80090288"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -2440,7 +2440,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="73382495"/>
+        <c:axId val="80090288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2516,7 +2516,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31899155"/>
+        <c:crossAx val="49003960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_USD_MONEY_MARKET.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_USD_MONEY_MARKET.xlsx
@@ -2393,11 +2393,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="49003960"/>
-        <c:axId val="80090288"/>
+        <c:axId val="40375593"/>
+        <c:axId val="60520738"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="49003960"/>
+        <c:axId val="40375593"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2429,7 +2429,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80090288"/>
+        <c:crossAx val="60520738"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -2440,7 +2440,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="80090288"/>
+        <c:axId val="60520738"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2516,7 +2516,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49003960"/>
+        <c:crossAx val="40375593"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_USD_MONEY_MARKET.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_USD_MONEY_MARKET.xlsx
@@ -2393,11 +2393,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="40375593"/>
-        <c:axId val="60520738"/>
+        <c:axId val="55261721"/>
+        <c:axId val="86284819"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="40375593"/>
+        <c:axId val="55261721"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2429,7 +2429,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60520738"/>
+        <c:crossAx val="86284819"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -2440,7 +2440,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="60520738"/>
+        <c:axId val="86284819"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2516,7 +2516,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40375593"/>
+        <c:crossAx val="55261721"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
